--- a/artfynd/A 39681-2023 artfynd.xlsx
+++ b/artfynd/A 39681-2023 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>117458847</v>
       </c>
       <c r="B4" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 39681-2023 artfynd.xlsx
+++ b/artfynd/A 39681-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117337524</v>
+        <v>117337450</v>
       </c>
       <c r="B2" t="n">
-        <v>78480</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -711,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stöåsen (Stöåsen), Vrm</t>
+          <t>Stöåsen, Stöåsen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>403633</v>
+        <v>403638</v>
       </c>
       <c r="R2" t="n">
-        <v>6694279</v>
+        <v>6694268</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,31 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117337540</v>
+        <v>117337524</v>
       </c>
       <c r="B3" t="n">
-        <v>78480</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -813,14 +803,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stöåsen (Stöåsen), Vrm</t>
+          <t>Stöåsen, Stöåsen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>403628</v>
+        <v>403633</v>
       </c>
       <c r="R3" t="n">
-        <v>6694314</v>
+        <v>6694279</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,31 +857,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117458847</v>
+        <v>117337540</v>
       </c>
       <c r="B4" t="n">
-        <v>78482</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -913,19 +898,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stöåsen, Vrm</t>
+          <t>Stöåsen, Stöåsen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403627</v>
+        <v>403628</v>
       </c>
       <c r="R4" t="n">
-        <v>6694302</v>
+        <v>6694314</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,22 +948,223 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>117339107</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stöåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>403594</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6694321</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>August Oljeqvist</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>August Oljeqvist, Julia Lea Falk, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>117458847</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stöåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>403627</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6694302</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
         <is>
           <t>August Oljeqvist, Jonas Göransson, Amanda Rudelius, Daniel Söderström, Svea Nikula</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39681-2023 artfynd.xlsx
+++ b/artfynd/A 39681-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117337450</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117337524</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117337540</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117339107</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,8 +1190,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117458847</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>